--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/136.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/136.xlsx
@@ -426,13 +426,13 @@
         <v>-17.3785836556771</v>
       </c>
       <c r="E2">
-        <v>-16.46383539084415</v>
+        <v>-12.76245998983073</v>
       </c>
       <c r="F2">
-        <v>1.953922232882062</v>
+        <v>3.231244887181233</v>
       </c>
       <c r="G2">
-        <v>-6.064288264415148</v>
+        <v>-3.015428107841191</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.30631227660604</v>
       </c>
       <c r="E3">
-        <v>-16.91115805332182</v>
+        <v>-13.1066919415238</v>
       </c>
       <c r="F3">
-        <v>1.89362039942787</v>
+        <v>3.271420706217009</v>
       </c>
       <c r="G3">
-        <v>-5.06881715239292</v>
+        <v>-2.574331020188698</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.11507009240712</v>
       </c>
       <c r="E4">
-        <v>-17.4639851032302</v>
+        <v>-14.81742715282345</v>
       </c>
       <c r="F4">
-        <v>1.960549172104459</v>
+        <v>3.269361384853649</v>
       </c>
       <c r="G4">
-        <v>-5.033784959496352</v>
+        <v>-2.508523995959065</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.81722184644497</v>
       </c>
       <c r="E5">
-        <v>-19.25742383533194</v>
+        <v>-15.92675837353444</v>
       </c>
       <c r="F5">
-        <v>2.287755952945069</v>
+        <v>3.314073343787156</v>
       </c>
       <c r="G5">
-        <v>-4.753216225043118</v>
+        <v>-1.722209840562452</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.41135658638237</v>
       </c>
       <c r="E6">
-        <v>-19.04254774366798</v>
+        <v>-17.9949758514736</v>
       </c>
       <c r="F6">
-        <v>1.686407607087185</v>
+        <v>3.491625612903202</v>
       </c>
       <c r="G6">
-        <v>-4.130989259300481</v>
+        <v>-1.499310809403323</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.91304761231871</v>
       </c>
       <c r="E7">
-        <v>-20.27396209515176</v>
+        <v>-17.32476169833839</v>
       </c>
       <c r="F7">
-        <v>1.903547554383019</v>
+        <v>3.796000931387852</v>
       </c>
       <c r="G7">
-        <v>-4.414179945820817</v>
+        <v>-0.9473435516406375</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.33066707670633</v>
       </c>
       <c r="E8">
-        <v>-20.08546436458248</v>
+        <v>-18.81706143740405</v>
       </c>
       <c r="F8">
-        <v>2.346851683460786</v>
+        <v>3.391422978390962</v>
       </c>
       <c r="G8">
-        <v>-3.680923903782103</v>
+        <v>-0.5688455695902235</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.66588630105596</v>
       </c>
       <c r="E9">
-        <v>-21.15368156977783</v>
+        <v>-18.25621446002809</v>
       </c>
       <c r="F9">
-        <v>2.04308438664979</v>
+        <v>3.27707845557813</v>
       </c>
       <c r="G9">
-        <v>-3.280761711722698</v>
+        <v>0.2911315346007136</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.93126535711203</v>
       </c>
       <c r="E10">
-        <v>-22.82741009148681</v>
+        <v>-20.00617078470817</v>
       </c>
       <c r="F10">
-        <v>1.890222436341586</v>
+        <v>3.684973191655828</v>
       </c>
       <c r="G10">
-        <v>-2.589453592212089</v>
+        <v>0.6828485249894375</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.11799410569348</v>
       </c>
       <c r="E11">
-        <v>-23.83015009100525</v>
+        <v>-21.15129053550179</v>
       </c>
       <c r="F11">
-        <v>1.965287433648472</v>
+        <v>3.238746582380985</v>
       </c>
       <c r="G11">
-        <v>-1.913062790901435</v>
+        <v>1.557759500108027</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.24423640146354</v>
       </c>
       <c r="E12">
-        <v>-23.42866917090722</v>
+        <v>-21.46129628064488</v>
       </c>
       <c r="F12">
-        <v>2.222826859178838</v>
+        <v>3.38469663508023</v>
       </c>
       <c r="G12">
-        <v>-1.598405369030327</v>
+        <v>2.421547042214665</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.30034889224748</v>
       </c>
       <c r="E13">
-        <v>-24.71903066854885</v>
+        <v>-22.38755941112179</v>
       </c>
       <c r="F13">
-        <v>2.36477258385295</v>
+        <v>3.679673297012717</v>
       </c>
       <c r="G13">
-        <v>-0.5924961069227768</v>
+        <v>2.995036156528152</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.30800638746778</v>
       </c>
       <c r="E14">
-        <v>-24.59166733708312</v>
+        <v>-24.71448860911915</v>
       </c>
       <c r="F14">
-        <v>2.696333263762674</v>
+        <v>4.031717846058868</v>
       </c>
       <c r="G14">
-        <v>-0.3480685981217673</v>
+        <v>3.866332015917857</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.269905663970826</v>
       </c>
       <c r="E15">
-        <v>-26.79956106731486</v>
+        <v>-24.26138308533368</v>
       </c>
       <c r="F15">
-        <v>2.741804007237145</v>
+        <v>3.855810714604782</v>
       </c>
       <c r="G15">
-        <v>0.3629438884385842</v>
+        <v>4.776655896670031</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.206561316035645</v>
       </c>
       <c r="E16">
-        <v>-27.49757552238316</v>
+        <v>-25.26980631973175</v>
       </c>
       <c r="F16">
-        <v>2.555827241634628</v>
+        <v>4.183118556268534</v>
       </c>
       <c r="G16">
-        <v>1.235126974032814</v>
+        <v>4.998813365628362</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.139439571306423</v>
       </c>
       <c r="E17">
-        <v>-28.34664628492532</v>
+        <v>-26.80468729989154</v>
       </c>
       <c r="F17">
-        <v>3.01817388056795</v>
+        <v>4.583118950997553</v>
       </c>
       <c r="G17">
-        <v>1.572607296851658</v>
+        <v>5.687502843617408</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.09426072238873</v>
       </c>
       <c r="E18">
-        <v>-29.03993754160362</v>
+        <v>-27.69474980915114</v>
       </c>
       <c r="F18">
-        <v>2.706212373408461</v>
+        <v>4.79921515536586</v>
       </c>
       <c r="G18">
-        <v>1.705201266790548</v>
+        <v>5.091968806557914</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.110684498729781</v>
       </c>
       <c r="E19">
-        <v>-29.37002254049673</v>
+        <v>-28.03402761027981</v>
       </c>
       <c r="F19">
-        <v>3.285731581467773</v>
+        <v>4.853168381044997</v>
       </c>
       <c r="G19">
-        <v>1.589805580928172</v>
+        <v>6.592440466777187</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.21526723962832</v>
       </c>
       <c r="E20">
-        <v>-29.90706785848838</v>
+        <v>-28.12926594713512</v>
       </c>
       <c r="F20">
-        <v>3.633985521278714</v>
+        <v>5.188100516284116</v>
       </c>
       <c r="G20">
-        <v>2.449448320019643</v>
+        <v>7.190755362089669</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.450312572954754</v>
       </c>
       <c r="E21">
-        <v>-30.43300935821322</v>
+        <v>-28.59539536216666</v>
       </c>
       <c r="F21">
-        <v>3.741721328952011</v>
+        <v>5.656679791556101</v>
       </c>
       <c r="G21">
-        <v>2.810973135090213</v>
+        <v>7.187865255833885</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.828188069627769</v>
       </c>
       <c r="E22">
-        <v>-31.04441221941082</v>
+        <v>-29.43210791914188</v>
       </c>
       <c r="F22">
-        <v>3.407809742353142</v>
+        <v>5.553215046211638</v>
       </c>
       <c r="G22">
-        <v>2.955332783875673</v>
+        <v>7.044290206341233</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.371920879501452</v>
       </c>
       <c r="E23">
-        <v>-30.58417208482626</v>
+        <v>-28.04968254492433</v>
       </c>
       <c r="F23">
-        <v>4.012605753341478</v>
+        <v>5.496944048539467</v>
       </c>
       <c r="G23">
-        <v>3.374057204773771</v>
+        <v>7.450775540380646</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.074756975656347</v>
       </c>
       <c r="E24">
-        <v>-31.30409303290667</v>
+        <v>-29.56046977912631</v>
       </c>
       <c r="F24">
-        <v>3.852248734772744</v>
+        <v>5.37564455301273</v>
       </c>
       <c r="G24">
-        <v>2.284275271428785</v>
+        <v>8.18207505000565</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.929071842590397</v>
       </c>
       <c r="E25">
-        <v>-30.9935121715646</v>
+        <v>-29.70112191756754</v>
       </c>
       <c r="F25">
-        <v>4.288351037650572</v>
+        <v>5.235734955414699</v>
       </c>
       <c r="G25">
-        <v>3.35375362898142</v>
+        <v>6.52897399824382</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.91238328867708</v>
       </c>
       <c r="E26">
-        <v>-31.5092691332462</v>
+        <v>-28.81024428298657</v>
       </c>
       <c r="F26">
-        <v>4.105548575935583</v>
+        <v>5.114765150114276</v>
       </c>
       <c r="G26">
-        <v>2.859432900694065</v>
+        <v>6.688095369588889</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.995613769500094</v>
       </c>
       <c r="E27">
-        <v>-30.7704033141547</v>
+        <v>-29.03139683962516</v>
       </c>
       <c r="F27">
-        <v>3.976532009684365</v>
+        <v>5.134003154676892</v>
       </c>
       <c r="G27">
-        <v>2.626817418377175</v>
+        <v>6.322435683139768</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.152759514869891</v>
       </c>
       <c r="E28">
-        <v>-30.58846281394853</v>
+        <v>-29.50069618646206</v>
       </c>
       <c r="F28">
-        <v>3.590156601996592</v>
+        <v>5.49993942506799</v>
       </c>
       <c r="G28">
-        <v>1.830399477994705</v>
+        <v>6.342302266920935</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.351404058383774</v>
       </c>
       <c r="E29">
-        <v>-30.95206984168341</v>
+        <v>-29.67994224463367</v>
       </c>
       <c r="F29">
-        <v>3.880066968893557</v>
+        <v>5.118620372006905</v>
       </c>
       <c r="G29">
-        <v>1.14834102272082</v>
+        <v>5.173375121368593</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.575394980346</v>
       </c>
       <c r="E30">
-        <v>-30.02539009159779</v>
+        <v>-28.67126541569117</v>
       </c>
       <c r="F30">
-        <v>3.391752668617277</v>
+        <v>5.210032371640636</v>
       </c>
       <c r="G30">
-        <v>1.308657501005566</v>
+        <v>5.609824203083949</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.801853915103782</v>
       </c>
       <c r="E31">
-        <v>-30.34295612409669</v>
+        <v>-28.33141702683753</v>
       </c>
       <c r="F31">
-        <v>3.926160644654932</v>
+        <v>5.637998449888167</v>
       </c>
       <c r="G31">
-        <v>0.6203222513892226</v>
+        <v>4.270245056073256</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.025603707992823</v>
       </c>
       <c r="E32">
-        <v>-30.59612952044351</v>
+        <v>-28.07975161233526</v>
       </c>
       <c r="F32">
-        <v>3.867303483951222</v>
+        <v>4.919272099788398</v>
       </c>
       <c r="G32">
-        <v>1.027406794171243</v>
+        <v>4.772875253664183</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.237055409455878</v>
       </c>
       <c r="E33">
-        <v>-29.27438116945473</v>
+        <v>-27.94448609372614</v>
       </c>
       <c r="F33">
-        <v>3.768204234819512</v>
+        <v>5.145893540376676</v>
       </c>
       <c r="G33">
-        <v>0.0297441010020177</v>
+        <v>3.943643185896457</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.43797756487497</v>
       </c>
       <c r="E34">
-        <v>-29.94333414257881</v>
+        <v>-27.45288854087547</v>
       </c>
       <c r="F34">
-        <v>4.246660963002478</v>
+        <v>5.043008652214172</v>
       </c>
       <c r="G34">
-        <v>0.05416599544522125</v>
+        <v>4.399088177916151</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.630107691290053</v>
       </c>
       <c r="E35">
-        <v>-28.96373690947656</v>
+        <v>-26.27529963144686</v>
       </c>
       <c r="F35">
-        <v>4.223862635342631</v>
+        <v>5.420411184194821</v>
       </c>
       <c r="G35">
-        <v>-0.7929297760524116</v>
+        <v>3.429873002565883</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.817660445909466</v>
       </c>
       <c r="E36">
-        <v>-28.24139549203905</v>
+        <v>-26.61971725057424</v>
       </c>
       <c r="F36">
-        <v>3.798285568684773</v>
+        <v>5.645904388380486</v>
       </c>
       <c r="G36">
-        <v>-1.981349413739982</v>
+        <v>3.027572198088109</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.00717590408565</v>
       </c>
       <c r="E37">
-        <v>-28.03367438930721</v>
+        <v>-26.26561775401846</v>
       </c>
       <c r="F37">
-        <v>4.143370174812603</v>
+        <v>5.618712400016189</v>
       </c>
       <c r="G37">
-        <v>-0.9865834479176189</v>
+        <v>3.256085914481842</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.197937578091864</v>
       </c>
       <c r="E38">
-        <v>-27.12879471309452</v>
+        <v>-24.4819061840852</v>
       </c>
       <c r="F38">
-        <v>4.175396515339637</v>
+        <v>6.092623047892592</v>
       </c>
       <c r="G38">
-        <v>-1.180833017979895</v>
+        <v>2.615674122091988</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.397164278169534</v>
       </c>
       <c r="E39">
-        <v>-26.39423547278432</v>
+        <v>-23.50341163440382</v>
       </c>
       <c r="F39">
-        <v>4.687985293987554</v>
+        <v>5.743139810855897</v>
       </c>
       <c r="G39">
-        <v>-1.143751597394518</v>
+        <v>2.799031997330062</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.601225495735213</v>
       </c>
       <c r="E40">
-        <v>-26.30763293586163</v>
+        <v>-24.0582402698236</v>
       </c>
       <c r="F40">
-        <v>4.352178402771079</v>
+        <v>5.8470303370454</v>
       </c>
       <c r="G40">
-        <v>-2.04708691651329</v>
+        <v>1.836030715957006</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.818407050490126</v>
       </c>
       <c r="E41">
-        <v>-25.78000231533193</v>
+        <v>-23.43234176332744</v>
       </c>
       <c r="F41">
-        <v>4.79734801523995</v>
+        <v>5.836273157952645</v>
       </c>
       <c r="G41">
-        <v>-2.147237540167322</v>
+        <v>2.887125614130068</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.044701670426803</v>
       </c>
       <c r="E42">
-        <v>-25.18894135937678</v>
+        <v>-22.84980339545474</v>
       </c>
       <c r="F42">
-        <v>4.543718483850798</v>
+        <v>5.795651677254163</v>
       </c>
       <c r="G42">
-        <v>-1.473955341118045</v>
+        <v>2.548433631643851</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.281715679633068</v>
       </c>
       <c r="E43">
-        <v>-24.1596690306474</v>
+        <v>-22.16319616641176</v>
       </c>
       <c r="F43">
-        <v>4.913922503101119</v>
+        <v>6.027808268827947</v>
       </c>
       <c r="G43">
-        <v>-2.149501953316184</v>
+        <v>2.418292775949561</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.523043751597612</v>
       </c>
       <c r="E44">
-        <v>-24.38382849402708</v>
+        <v>-21.91145376785136</v>
       </c>
       <c r="F44">
-        <v>4.67373074772018</v>
+        <v>5.986146358671549</v>
       </c>
       <c r="G44">
-        <v>-2.391575664238772</v>
+        <v>1.872516238345314</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.761850861160321</v>
       </c>
       <c r="E45">
-        <v>-23.02150048745556</v>
+        <v>-20.92068252513518</v>
       </c>
       <c r="F45">
-        <v>4.671300317760366</v>
+        <v>6.116077442535457</v>
       </c>
       <c r="G45">
-        <v>-1.750382583101649</v>
+        <v>1.309382510478667</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.993959578383738</v>
       </c>
       <c r="E46">
-        <v>-22.53818098509091</v>
+        <v>-19.89570771823907</v>
       </c>
       <c r="F46">
-        <v>4.819699024502286</v>
+        <v>5.983606584214566</v>
       </c>
       <c r="G46">
-        <v>-1.910629539930071</v>
+        <v>2.053493831340651</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.208830575494257</v>
       </c>
       <c r="E47">
-        <v>-22.45238451654159</v>
+        <v>-19.23678757927899</v>
       </c>
       <c r="F47">
-        <v>4.886331241648673</v>
+        <v>6.197935052545298</v>
       </c>
       <c r="G47">
-        <v>-1.428385681769977</v>
+        <v>1.790371671879377</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.410283064555613</v>
       </c>
       <c r="E48">
-        <v>-21.16798701916807</v>
+        <v>-19.0893721649073</v>
       </c>
       <c r="F48">
-        <v>4.767178874429992</v>
+        <v>6.367690727666195</v>
       </c>
       <c r="G48">
-        <v>-2.491381991156719</v>
+        <v>1.206768840943417</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.590004089770381</v>
       </c>
       <c r="E49">
-        <v>-20.94387284052846</v>
+        <v>-17.98018585536455</v>
       </c>
       <c r="F49">
-        <v>5.098994691499779</v>
+        <v>6.221086264718739</v>
       </c>
       <c r="G49">
-        <v>-2.103932293968116</v>
+        <v>0.6806635649335185</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.759026103595479</v>
       </c>
       <c r="E50">
-        <v>-20.94626840327852</v>
+        <v>-18.13186709225147</v>
       </c>
       <c r="F50">
-        <v>5.090674569306061</v>
+        <v>6.244379956085461</v>
       </c>
       <c r="G50">
-        <v>-1.583497982466989</v>
+        <v>0.9755404772074817</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.915365329453046</v>
       </c>
       <c r="E51">
-        <v>-20.31468666190274</v>
+        <v>-17.73368290123102</v>
       </c>
       <c r="F51">
-        <v>4.945846126070206</v>
+        <v>6.278450707362604</v>
       </c>
       <c r="G51">
-        <v>-2.724881389132594</v>
+        <v>0.7359298121661116</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.069263599336234</v>
       </c>
       <c r="E52">
-        <v>-19.40234406052541</v>
+        <v>-16.90956855894513</v>
       </c>
       <c r="F52">
-        <v>4.74402434878694</v>
+        <v>6.614428242264056</v>
       </c>
       <c r="G52">
-        <v>-2.42360850287676</v>
+        <v>0.70100686727234</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.222719838378562</v>
       </c>
       <c r="E53">
-        <v>-19.5940343652701</v>
+        <v>-16.12535912961483</v>
       </c>
       <c r="F53">
-        <v>4.914552062327247</v>
+        <v>6.755013787662771</v>
       </c>
       <c r="G53">
-        <v>-2.169964435294419</v>
+        <v>-0.1119207637144749</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.379289398441904</v>
       </c>
       <c r="E54">
-        <v>-18.75765238689743</v>
+        <v>-16.1253998858809</v>
       </c>
       <c r="F54">
-        <v>4.969449626845575</v>
+        <v>6.117139409545846</v>
       </c>
       <c r="G54">
-        <v>-3.447374847623138</v>
+        <v>-0.2624446482940573</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.543420707655033</v>
       </c>
       <c r="E55">
-        <v>-19.21758232101246</v>
+        <v>-15.64164112153751</v>
       </c>
       <c r="F55">
-        <v>4.885304066069202</v>
+        <v>6.115138073900682</v>
       </c>
       <c r="G55">
-        <v>-3.203377709742234</v>
+        <v>-0.1146850692397664</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.709582907264275</v>
       </c>
       <c r="E56">
-        <v>-18.66062077433507</v>
+        <v>-14.49600512470702</v>
       </c>
       <c r="F56">
-        <v>4.714829368042674</v>
+        <v>6.569529072297517</v>
       </c>
       <c r="G56">
-        <v>-3.458345995540283</v>
+        <v>-0.4443657467680875</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.885949512277326</v>
       </c>
       <c r="E57">
-        <v>-17.41451605317041</v>
+        <v>-14.20935272002149</v>
       </c>
       <c r="F57">
-        <v>4.84876312319691</v>
+        <v>6.336660084757326</v>
       </c>
       <c r="G57">
-        <v>-3.922080593590312</v>
+        <v>-1.21319691117181</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.061403587518333</v>
       </c>
       <c r="E58">
-        <v>-18.27147088895993</v>
+        <v>-13.68513656889357</v>
       </c>
       <c r="F58">
-        <v>5.117626331123546</v>
+        <v>6.353035251575867</v>
       </c>
       <c r="G58">
-        <v>-3.926278365334108</v>
+        <v>-0.8898559283511933</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.246514634869586</v>
       </c>
       <c r="E59">
-        <v>-17.17099736340794</v>
+        <v>-12.93508089052912</v>
       </c>
       <c r="F59">
-        <v>4.71709743799154</v>
+        <v>6.437011825402069</v>
       </c>
       <c r="G59">
-        <v>-4.297453420651655</v>
+        <v>-0.9339159789333535</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.431409728879713</v>
       </c>
       <c r="E60">
-        <v>-16.72382866904652</v>
+        <v>-13.81204252448452</v>
       </c>
       <c r="F60">
-        <v>4.957637107681655</v>
+        <v>6.152964642982119</v>
       </c>
       <c r="G60">
-        <v>-4.349432296163751</v>
+        <v>-1.640320186103039</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.621980515408865</v>
       </c>
       <c r="E61">
-        <v>-16.2331458679454</v>
+        <v>-12.09566936304532</v>
       </c>
       <c r="F61">
-        <v>4.770409507300911</v>
+        <v>6.451929065591683</v>
       </c>
       <c r="G61">
-        <v>-4.583732846160131</v>
+        <v>-2.551667025426847</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.812936841984117</v>
       </c>
       <c r="E62">
-        <v>-16.091218964071</v>
+        <v>-13.26192803050673</v>
       </c>
       <c r="F62">
-        <v>4.606303297867106</v>
+        <v>6.310144044193714</v>
       </c>
       <c r="G62">
-        <v>-4.815050594625626</v>
+        <v>-1.915380172778925</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.003087807401421</v>
       </c>
       <c r="E63">
-        <v>-15.75613000139943</v>
+        <v>-10.90006165554019</v>
       </c>
       <c r="F63">
-        <v>4.861039528106398</v>
+        <v>6.237678463796813</v>
       </c>
       <c r="G63">
-        <v>-4.881801124333951</v>
+        <v>-1.982974891599764</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.192157315493384</v>
       </c>
       <c r="E64">
-        <v>-15.36049986971931</v>
+        <v>-11.29874850717549</v>
       </c>
       <c r="F64">
-        <v>4.660914247264066</v>
+        <v>6.021996443129906</v>
       </c>
       <c r="G64">
-        <v>-5.243570919774428</v>
+        <v>-2.834609421031738</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.369352378705264</v>
       </c>
       <c r="E65">
-        <v>-15.7374545745918</v>
+        <v>-11.34419627231647</v>
       </c>
       <c r="F65">
-        <v>4.506644072371103</v>
+        <v>5.957353964485043</v>
       </c>
       <c r="G65">
-        <v>-5.697301049204779</v>
+        <v>-2.126228818175107</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.537151939468629</v>
       </c>
       <c r="E66">
-        <v>-14.46237667672606</v>
+        <v>-11.9971841103265</v>
       </c>
       <c r="F66">
-        <v>4.733981222395399</v>
+        <v>5.845014090786986</v>
       </c>
       <c r="G66">
-        <v>-5.655604728137659</v>
+        <v>-2.785557067776357</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.67727686596967</v>
       </c>
       <c r="E67">
-        <v>-14.46929618500978</v>
+        <v>-11.38626579584773</v>
       </c>
       <c r="F67">
-        <v>4.3188664360349</v>
+        <v>5.474997282569697</v>
       </c>
       <c r="G67">
-        <v>-5.238866634563124</v>
+        <v>-2.246699570349186</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.794122324022322</v>
       </c>
       <c r="E68">
-        <v>-14.83046010101752</v>
+        <v>-11.10927262622055</v>
       </c>
       <c r="F68">
-        <v>4.573105645832513</v>
+        <v>5.80183792501827</v>
       </c>
       <c r="G68">
-        <v>-5.776217833769926</v>
+        <v>-2.963743870882089</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.87075781339451</v>
       </c>
       <c r="E69">
-        <v>-14.23978859382704</v>
+        <v>-9.592962917966219</v>
       </c>
       <c r="F69">
-        <v>4.027922266619241</v>
+        <v>5.644055472337437</v>
       </c>
       <c r="G69">
-        <v>-4.991621851508194</v>
+        <v>-3.030292457312519</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.90878392152432</v>
       </c>
       <c r="E70">
-        <v>-12.88316646450519</v>
+        <v>-10.87577092096305</v>
       </c>
       <c r="F70">
-        <v>4.401009004431304</v>
+        <v>5.226087788641696</v>
       </c>
       <c r="G70">
-        <v>-5.64987748435472</v>
+        <v>-2.495046765068692</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.89970707884456</v>
       </c>
       <c r="E71">
-        <v>-14.17971838611529</v>
+        <v>-11.38937232901699</v>
       </c>
       <c r="F71">
-        <v>4.249271977056102</v>
+        <v>4.839217017247049</v>
       </c>
       <c r="G71">
-        <v>-5.507917981085232</v>
+        <v>-2.386791925934525</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.842611277676866</v>
       </c>
       <c r="E72">
-        <v>-13.80148212309864</v>
+        <v>-9.942257703599857</v>
       </c>
       <c r="F72">
-        <v>3.86084056147458</v>
+        <v>4.856854615987456</v>
       </c>
       <c r="G72">
-        <v>-5.35871169363028</v>
+        <v>-2.828173720503395</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.73876184209835</v>
       </c>
       <c r="E73">
-        <v>-13.53879440286169</v>
+        <v>-9.90518308689906</v>
       </c>
       <c r="F73">
-        <v>4.142447373525884</v>
+        <v>5.098000650616419</v>
       </c>
       <c r="G73">
-        <v>-5.716296959509117</v>
+        <v>-2.438893291631575</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.584027118482306</v>
       </c>
       <c r="E74">
-        <v>-13.78306029083543</v>
+        <v>-10.11019616217431</v>
       </c>
       <c r="F74">
-        <v>3.964790730117085</v>
+        <v>4.837873405319708</v>
       </c>
       <c r="G74">
-        <v>-5.671346372176894</v>
+        <v>-1.981306376647972</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.387867521534851</v>
       </c>
       <c r="E75">
-        <v>-14.71565422797507</v>
+        <v>-10.23646813140419</v>
       </c>
       <c r="F75">
-        <v>3.938776680199569</v>
+        <v>5.276444243057878</v>
       </c>
       <c r="G75">
-        <v>-5.250023173030467</v>
+        <v>-2.018301723049327</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.143306999425077</v>
       </c>
       <c r="E76">
-        <v>-14.07263808972992</v>
+        <v>-10.82737964771708</v>
       </c>
       <c r="F76">
-        <v>3.867730921531067</v>
+        <v>4.539295001919848</v>
       </c>
       <c r="G76">
-        <v>-5.648410912680823</v>
+        <v>-1.523858504577018</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.864408139620325</v>
       </c>
       <c r="E77">
-        <v>-14.6863912289375</v>
+        <v>-11.16258635071286</v>
       </c>
       <c r="F77">
-        <v>3.72658871323767</v>
+        <v>4.815605232797651</v>
       </c>
       <c r="G77">
-        <v>-5.330015884895877</v>
+        <v>-1.72130606163023</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.545922119688464</v>
       </c>
       <c r="E78">
-        <v>-14.95607091304228</v>
+        <v>-11.20305732291941</v>
       </c>
       <c r="F78">
-        <v>3.54296948126352</v>
+        <v>4.303906120740341</v>
       </c>
       <c r="G78">
-        <v>-5.171414269200473</v>
+        <v>-0.9487505334948277</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.200058213131209</v>
       </c>
       <c r="E79">
-        <v>-15.57608693180247</v>
+        <v>-12.08285378160361</v>
       </c>
       <c r="F79">
-        <v>3.723164242394497</v>
+        <v>4.65062426738649</v>
       </c>
       <c r="G79">
-        <v>-4.757874162616873</v>
+        <v>-0.5317178013672971</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.828191493872446</v>
       </c>
       <c r="E80">
-        <v>-14.83189109880395</v>
+        <v>-12.18243492503228</v>
       </c>
       <c r="F80">
-        <v>3.184211842785083</v>
+        <v>4.462654449812838</v>
       </c>
       <c r="G80">
-        <v>-4.403112792083034</v>
+        <v>-0.6847908060121183</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.438477735689779</v>
       </c>
       <c r="E81">
-        <v>-16.15885172337556</v>
+        <v>-12.26647887414064</v>
       </c>
       <c r="F81">
-        <v>3.4975136484023</v>
+        <v>4.242807397844655</v>
       </c>
       <c r="G81">
-        <v>-4.234404080856235</v>
+        <v>0.3014339523189255</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.039867624682206</v>
       </c>
       <c r="E82">
-        <v>-16.85028630571072</v>
+        <v>-12.38687288410856</v>
       </c>
       <c r="F82">
-        <v>3.203130097530218</v>
+        <v>4.088094874758597</v>
       </c>
       <c r="G82">
-        <v>-4.496360928287685</v>
+        <v>-0.1065907853962483</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.635930521335593</v>
       </c>
       <c r="E83">
-        <v>-17.61734187549996</v>
+        <v>-12.9046042604575</v>
       </c>
       <c r="F83">
-        <v>3.328006483502243</v>
+        <v>3.943188564986879</v>
       </c>
       <c r="G83">
-        <v>-4.199745979605605</v>
+        <v>-0.07044955974402477</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.239543956128117</v>
       </c>
       <c r="E84">
-        <v>-18.4142083896817</v>
+        <v>-15.19620683272103</v>
       </c>
       <c r="F84">
-        <v>3.180909970317524</v>
+        <v>4.018273443111432</v>
       </c>
       <c r="G84">
-        <v>-3.737577269595651</v>
+        <v>0.03189926614808324</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.848269379775561</v>
       </c>
       <c r="E85">
-        <v>-18.64338993073589</v>
+        <v>-15.21995415041725</v>
       </c>
       <c r="F85">
-        <v>3.036701145898963</v>
+        <v>4.099519717978008</v>
       </c>
       <c r="G85">
-        <v>-3.37082841366411</v>
+        <v>0.4794419859655372</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.47521188342975</v>
       </c>
       <c r="E86">
-        <v>-19.72847570160981</v>
+        <v>-16.5361913485387</v>
       </c>
       <c r="F86">
-        <v>2.870066759151815</v>
+        <v>3.958198582325606</v>
       </c>
       <c r="G86">
-        <v>-3.25468123396432</v>
+        <v>1.249183550392559</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.115693787807412</v>
       </c>
       <c r="E87">
-        <v>-21.21424538115642</v>
+        <v>-17.28784104975385</v>
       </c>
       <c r="F87">
-        <v>2.757125490719325</v>
+        <v>3.703029944302052</v>
       </c>
       <c r="G87">
-        <v>-2.856968845603975</v>
+        <v>1.91068682841311</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.779188039741229</v>
       </c>
       <c r="E88">
-        <v>-22.23445170492245</v>
+        <v>-19.41488340505265</v>
       </c>
       <c r="F88">
-        <v>2.577190836952827</v>
+        <v>3.666762362672684</v>
       </c>
       <c r="G88">
-        <v>-2.608641514157704</v>
+        <v>1.085450589111285</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.464224761020309</v>
       </c>
       <c r="E89">
-        <v>-23.96186075751835</v>
+        <v>-19.60732543648261</v>
       </c>
       <c r="F89">
-        <v>2.427617505233737</v>
+        <v>3.0806526635567</v>
       </c>
       <c r="G89">
-        <v>-2.878417870152914</v>
+        <v>1.44881937804723</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.175320190220626</v>
       </c>
       <c r="E90">
-        <v>-25.38331704920802</v>
+        <v>-21.51974529466188</v>
       </c>
       <c r="F90">
-        <v>1.98548800113314</v>
+        <v>3.179796644528161</v>
       </c>
       <c r="G90">
-        <v>-2.429696596123479</v>
+        <v>2.233839110137989</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.916591250338431</v>
       </c>
       <c r="E91">
-        <v>-26.5054547944127</v>
+        <v>-23.71024968470417</v>
       </c>
       <c r="F91">
-        <v>2.061916491185034</v>
+        <v>2.668152204719435</v>
       </c>
       <c r="G91">
-        <v>-2.664017009393094</v>
+        <v>2.084271973219256</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.688618066810026</v>
       </c>
       <c r="E92">
-        <v>-28.20123698453903</v>
+        <v>-24.25761086648529</v>
       </c>
       <c r="F92">
-        <v>2.152768514454473</v>
+        <v>2.613261267140329</v>
       </c>
       <c r="G92">
-        <v>-1.517224171316319</v>
+        <v>1.566006069046351</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.498736171853809</v>
       </c>
       <c r="E93">
-        <v>-29.6620751504364</v>
+        <v>-26.91735573320238</v>
       </c>
       <c r="F93">
-        <v>1.204329256619179</v>
+        <v>2.259773702078502</v>
       </c>
       <c r="G93">
-        <v>-1.979167764229603</v>
+        <v>1.902069478374387</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.342709204396014</v>
       </c>
       <c r="E94">
-        <v>-32.04429928030443</v>
+        <v>-28.57634407201639</v>
       </c>
       <c r="F94">
-        <v>0.9065361455171732</v>
+        <v>1.569795014325487</v>
       </c>
       <c r="G94">
-        <v>-2.126265234176039</v>
+        <v>2.138445740423889</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.225914703815002</v>
       </c>
       <c r="E95">
-        <v>-34.55769745251564</v>
+        <v>-31.23544136695038</v>
       </c>
       <c r="F95">
-        <v>0.5476907000940385</v>
+        <v>1.600830627438773</v>
       </c>
       <c r="G95">
-        <v>-1.889538054299374</v>
+        <v>1.932182200599598</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.141282911387142</v>
       </c>
       <c r="E96">
-        <v>-36.34857759680305</v>
+        <v>-32.96622413268199</v>
       </c>
       <c r="F96">
-        <v>0.4033277993385576</v>
+        <v>0.7943254971339522</v>
       </c>
       <c r="G96">
-        <v>-1.614355577438536</v>
+        <v>1.298742417115449</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.086576399691912</v>
       </c>
       <c r="E97">
-        <v>-38.86501890354741</v>
+        <v>-35.52740676262214</v>
       </c>
       <c r="F97">
-        <v>-0.5076369455614896</v>
+        <v>0.4402564181553595</v>
       </c>
       <c r="G97">
-        <v>-2.769980951014086</v>
+        <v>1.538194175970934</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.059487770967236</v>
       </c>
       <c r="E98">
-        <v>-40.96458927127868</v>
+        <v>-37.82444576793188</v>
       </c>
       <c r="F98">
-        <v>-0.8654941486730844</v>
+        <v>0.3706056301931714</v>
       </c>
       <c r="G98">
-        <v>-3.0239262782405</v>
+        <v>0.8756580077421307</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.048983644486478</v>
       </c>
       <c r="E99">
-        <v>-44.64183243430521</v>
+        <v>-40.21290787074548</v>
       </c>
       <c r="F99">
-        <v>-1.15552297210865</v>
+        <v>-0.1414024629053834</v>
       </c>
       <c r="G99">
-        <v>-2.751925235642901</v>
+        <v>1.297709526907197</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.066630479891918</v>
       </c>
       <c r="E100">
-        <v>-46.07838665833646</v>
+        <v>-43.52665495365031</v>
       </c>
       <c r="F100">
-        <v>-1.413288541939981</v>
+        <v>-0.6775003084447506</v>
       </c>
       <c r="G100">
-        <v>-2.594234019970796</v>
+        <v>1.218508035425673</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.091277346674011</v>
       </c>
       <c r="E101">
-        <v>-47.41784813540625</v>
+        <v>-45.66568870812143</v>
       </c>
       <c r="F101">
-        <v>-2.266252658030812</v>
+        <v>-1.313412284184444</v>
       </c>
       <c r="G101">
-        <v>-3.330360304992059</v>
+        <v>1.069096494147285</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.165568145672828</v>
       </c>
       <c r="E102">
-        <v>-51.28070439105917</v>
+        <v>-47.91875396657968</v>
       </c>
       <c r="F102">
-        <v>-2.620859347453822</v>
+        <v>-1.422668974409282</v>
       </c>
       <c r="G102">
-        <v>-2.935415532702546</v>
+        <v>0.9174271608111153</v>
       </c>
     </row>
   </sheetData>
